--- a/config/yunying/vipaward.xlsx
+++ b/config/yunying/vipaward.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="vipaward" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vipaward" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>vip1は受取可</t>
+          <t>vip1可以接受</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>vip2は受取可</t>
+          <t>vip2可以接受</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>vip3は受取可</t>
+          <t>vip3可以接受</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>vip4は受取可</t>
+          <t>vip4可以接受</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>vip5は受取可</t>
+          <t>vip5可以接受</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>vip6は受取可</t>
+          <t>vip6可以接受</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>vip7は受取可</t>
+          <t>vip7可以接受</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>vip8は受取可</t>
+          <t>vip8可以接受</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>vip9は受取可</t>
+          <t>vip9可以接受</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>vip10は受取可</t>
+          <t>vip10可以接受</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>vip11は受取可</t>
+          <t>vip11可以接受</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>vip12は受取可</t>
+          <t>vip12可以接受</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>vip13は受取可</t>
+          <t>vip13可以接受</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>vip14は受取可</t>
+          <t>vip14可以接受</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>vip15は受取可</t>
+          <t>vip15可以接受</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
